--- a/docs/base/0.3.0/StructureDefinition-appointment-lt.xlsx
+++ b/docs/base/0.3.0/StructureDefinition-appointment-lt.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T18:57:53+02:00</t>
+    <t>2026-03-15T22:56:00+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
